--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.999674001202224</v>
+        <v>0.4874470251953615</v>
       </c>
       <c r="D2" t="n">
-        <v>3.32126566866582</v>
+        <v>0.5397056711581958</v>
       </c>
       <c r="E2" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F2" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.45635138067034</v>
+        <v>10.63665709935893</v>
       </c>
       <c r="D3" t="n">
-        <v>39.07609298642714</v>
+        <v>6.34986511029441</v>
       </c>
       <c r="E3" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F3" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.11991483203216</v>
+        <v>8.956986160205226</v>
       </c>
       <c r="D4" t="n">
-        <v>26.85335375162198</v>
+        <v>4.363669984638572</v>
       </c>
       <c r="E4" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F4" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.47858987050458</v>
+        <v>11.12777085395699</v>
       </c>
       <c r="D5" t="n">
-        <v>46.69748739277292</v>
+        <v>7.5883417013256</v>
       </c>
       <c r="E5" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F5" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.34061745774197</v>
+        <v>7.85535033688307</v>
       </c>
       <c r="D6" t="n">
-        <v>40.55992738837887</v>
+        <v>6.590988200611568</v>
       </c>
       <c r="E6" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F6" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.22242842869643</v>
+        <v>8.973644619663171</v>
       </c>
       <c r="D7" t="n">
-        <v>50.9051461075082</v>
+        <v>8.272086242470083</v>
       </c>
       <c r="E7" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F7" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.4692000843214</v>
+        <v>6.413745013702227</v>
       </c>
       <c r="D8" t="n">
-        <v>39.33107519806361</v>
+        <v>6.391299719685336</v>
       </c>
       <c r="E8" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F8" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.30620842239527</v>
+        <v>4.274758868639232</v>
       </c>
       <c r="D9" t="n">
-        <v>27.19069510378059</v>
+        <v>4.418487954364346</v>
       </c>
       <c r="E9" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F9" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.86769327488315</v>
+        <v>4.853500157168511</v>
       </c>
       <c r="D10" t="n">
-        <v>30.11664774929854</v>
+        <v>4.893955259261013</v>
       </c>
       <c r="E10" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F10" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.49101065177179</v>
+        <v>7.717289230912916</v>
       </c>
       <c r="D11" t="n">
-        <v>46.01389005698596</v>
+        <v>7.47725713426022</v>
       </c>
       <c r="E11" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F11" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.39153221582978</v>
+        <v>4.613623985072339</v>
       </c>
       <c r="D12" t="n">
-        <v>28.00171075110702</v>
+        <v>4.550277997054891</v>
       </c>
       <c r="E12" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F12" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>82.45967402593314</v>
+        <v>13.39969702921413</v>
       </c>
       <c r="D13" t="n">
-        <v>80.65928721105804</v>
+        <v>13.10713417179693</v>
       </c>
       <c r="E13" t="n">
-        <v>20.8934349788558</v>
+        <v>3.395183184064068</v>
       </c>
       <c r="F13" t="n">
-        <v>17.65622220000781</v>
+        <v>2.869136107501269</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
